--- a/input/old/Metadata _Material conversions_ 10K+ nominal value change_SW_10_02_MAT_CONV.xlsx
+++ b/input/old/Metadata _Material conversions_ 10K+ nominal value change_SW_10_02_MAT_CONV.xlsx
@@ -422,7 +422,7 @@
         <v>Created on</v>
       </c>
       <c r="B6" t="str">
-        <v>16.01.2026 at 16:25 by ILIYAR</v>
+        <v>16.01.2026 at 16:25 by REDACTED</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>Updated on</v>
       </c>
       <c r="B7" t="str">
-        <v>20.01.2026 at 21:26 by ILIYAR</v>
+        <v>20.01.2026 at 21:26 by REDACTED</v>
       </c>
     </row>
     <row r="8">
